--- a/LastFPS/Excel/Localize.xlsx
+++ b/LastFPS/Excel/Localize.xlsx
@@ -120,9 +120,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -427,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3661,7 +3659,6 @@
           <t>모듈이 없습니다.</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>No modules equipped.</t>
@@ -3684,7 +3681,6 @@
           <t>장비가 없습니다.</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>No equipment equipped.</t>
@@ -3914,6 +3910,295 @@
       <c r="C134" t="inlineStr">
         <is>
           <t>퀘스트 목록 서브 그룹 헤더</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Quest.Status.AvailableFromNPCFormat</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>{0}에게서 수락 가능</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>퀘스트 제공 NPC 안내 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Welcome</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>귀환 신고</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Q_Welcome NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Mobility</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>기동 규격</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Q_Mobility NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Endurance</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>지구력 보강</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Q_Endurance NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Arsenal</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>무장 확충</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Q_Arsenal NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Fortress</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>철벽 확보</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Q_Fortress NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Apex</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>병기 조달</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Q_Apex NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_FirstSync</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>각성 완료</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Q_FirstSync NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Contamination</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>사격조 제압</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Q_Contamination NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Quest_Reach</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>정찰 보고</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Quest_Reach NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Quest_Hunt</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>돌격조 소탕</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Quest_Hunt NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Quest_Talk</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>교전 보고</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Quest_Talk NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Dungeon_Gate</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>궤도 돌파</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Q_Dungeon_Gate NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Quest_Defend</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>반응로 방어</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Quest_Defend NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Quest_Capture</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>기지 점령</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Quest_Capture NPC 상호작용 퀘스트 버튼 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Quest.Reward.PurchaseRefundFormat</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>구매액 환급 +{0}</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>퀘스트 구매액 환급 표시 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Quest.Reward.CompletionBonusFormat</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>완료 보너스 +{0}</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>퀘스트 고정 완료 보너스 표시 형식</t>
         </is>
       </c>
     </row>
